--- a/Pruebas calificadas/COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) _501_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) _501_CALIFICADO.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) _501_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) _501_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1309,11 +1301,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -1321,7 +1309,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1558,11 +1546,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -1570,7 +1554,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1811,11 +1795,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -1823,7 +1803,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2060,11 +2040,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -2072,7 +2048,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2309,11 +2285,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -2321,7 +2293,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2558,11 +2530,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -2570,7 +2538,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2807,11 +2775,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -2819,7 +2783,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3056,11 +3020,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -3068,7 +3028,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3309,11 +3269,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -3321,7 +3277,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3558,11 +3514,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -3570,7 +3522,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3811,11 +3763,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -3823,7 +3771,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4064,11 +4012,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -4076,7 +4020,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4313,11 +4257,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -4325,7 +4265,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4566,11 +4506,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -4578,7 +4514,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4819,11 +4755,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -4831,7 +4763,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5072,11 +5004,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -5084,7 +5012,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5325,11 +5253,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -5337,7 +5261,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5578,11 +5502,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -5590,7 +5510,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5831,11 +5751,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -5843,7 +5759,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6084,11 +6000,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -6096,7 +6008,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
